--- a/task-reviews/puzzles/task_puzzles_arithmetic_grid_value/task_puzzles_arithmetic_grid_value.xlsx
+++ b/task-reviews/puzzles/task_puzzles_arithmetic_grid_value/task_puzzles_arithmetic_grid_value.xlsx
@@ -4327,12 +4327,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0013.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0013.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0013.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0013.json</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0009.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0009.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0009.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0009.json</t>
         </is>
       </c>
     </row>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0021.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0021.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0021.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0021.json</t>
         </is>
       </c>
     </row>
@@ -4519,12 +4519,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0006.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0006.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0006.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0006.json</t>
         </is>
       </c>
     </row>
@@ -4583,12 +4583,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0000.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0000.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0000.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0000.json</t>
         </is>
       </c>
     </row>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0017.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0017.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0017.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0017.json</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0024.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0024.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0024.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0024.json</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0014.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0014.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0014.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0014.json</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0012.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0012.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0012.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0012.json</t>
         </is>
       </c>
     </row>
@@ -4903,12 +4903,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0001.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0001.png</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0001.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0001.json</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0002.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0002.png</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0002.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0002.json</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0008.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0008.png</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0008.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0008.json</t>
         </is>
       </c>
     </row>
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0007.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0007.png</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0007.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0007.json</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0019.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0019.png</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0019.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0019.json</t>
         </is>
       </c>
     </row>
@@ -5223,12 +5223,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0015.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0015.png</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0015.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0015.json</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0023.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0023.png</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0023.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0023.json</t>
         </is>
       </c>
     </row>
@@ -5351,12 +5351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0011.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0011.png</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0011.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0011.json</t>
         </is>
       </c>
     </row>
@@ -5415,12 +5415,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0016.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0016.png</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0016.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0016.json</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0018.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0018.png</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0018.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0018.json</t>
         </is>
       </c>
     </row>
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0010.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0010.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0010.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0010.json</t>
         </is>
       </c>
     </row>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0020.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0020.png</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0020.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0020.json</t>
         </is>
       </c>
     </row>
@@ -5671,12 +5671,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0004.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0004.png</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0004.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0004.json</t>
         </is>
       </c>
     </row>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0022.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0022.png</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0022.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0022.json</t>
         </is>
       </c>
     </row>
@@ -5799,12 +5799,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0003.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0003.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0003.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0003.json</t>
         </is>
       </c>
     </row>
@@ -5863,12 +5863,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0005.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0005.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0005.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0005.json</t>
         </is>
       </c>
     </row>
@@ -6024,12 +6024,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0004.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0004.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0004.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0004.json</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0001.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0001.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0001.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0001.json</t>
         </is>
       </c>
     </row>
@@ -6152,12 +6152,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0012.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0012.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0012.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0012.json</t>
         </is>
       </c>
     </row>
@@ -6216,12 +6216,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0002.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0002.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0002.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0002.json</t>
         </is>
       </c>
     </row>
@@ -6280,12 +6280,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0024.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0024.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0024.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0024.json</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0022.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0022.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0022.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0022.json</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0018.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0018.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0018.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0018.json</t>
         </is>
       </c>
     </row>
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0021.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0021.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0021.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0021.json</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0007.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0007.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0007.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0007.json</t>
         </is>
       </c>
     </row>
@@ -6600,12 +6600,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0010.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0010.png</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0010.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0010.json</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0008.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0008.png</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0008.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0008.json</t>
         </is>
       </c>
     </row>
@@ -6728,12 +6728,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0003.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0003.png</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0003.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0003.json</t>
         </is>
       </c>
     </row>
@@ -6792,12 +6792,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0014.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0014.png</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0014.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0014.json</t>
         </is>
       </c>
     </row>
@@ -6856,12 +6856,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0009.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0009.png</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0009.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0009.json</t>
         </is>
       </c>
     </row>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0019.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0019.png</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0019.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0019.json</t>
         </is>
       </c>
     </row>
@@ -6984,12 +6984,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0016.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0016.png</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0016.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0016.json</t>
         </is>
       </c>
     </row>
@@ -7048,12 +7048,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0013.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0013.png</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0013.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0013.json</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0005.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0005.png</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0005.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0005.json</t>
         </is>
       </c>
     </row>
@@ -7176,12 +7176,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0000.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0000.png</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0000.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0000.json</t>
         </is>
       </c>
     </row>
@@ -7240,12 +7240,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0015.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0015.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0015.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0015.json</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0011.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0011.png</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0011.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0011.json</t>
         </is>
       </c>
     </row>
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0020.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0020.png</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0020.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0020.json</t>
         </is>
       </c>
     </row>
@@ -7432,12 +7432,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0017.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0017.png</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0017.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0017.json</t>
         </is>
       </c>
     </row>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0023.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0023.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0023.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0023.json</t>
         </is>
       </c>
     </row>
@@ -7560,12 +7560,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/product_rule_missing/0006.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0006.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/product_rule_missing/0006.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0006.json</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0015.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0015.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0015.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0015.json</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0024.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0024.png</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0024.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0024.json</t>
         </is>
       </c>
     </row>
@@ -7849,12 +7849,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0001.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0001.png</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0001.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0001.json</t>
         </is>
       </c>
     </row>
@@ -7913,12 +7913,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0021.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0021.png</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0021.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0021.json</t>
         </is>
       </c>
     </row>
@@ -7977,12 +7977,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0008.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0008.png</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0008.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0008.json</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0002.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0002.png</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0002.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0002.json</t>
         </is>
       </c>
     </row>
@@ -8105,12 +8105,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0016.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0016.png</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0016.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0016.json</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0004.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0004.png</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0004.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0004.json</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0023.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0023.png</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0023.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0023.json</t>
         </is>
       </c>
     </row>
@@ -8297,12 +8297,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0019.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0019.png</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0019.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0019.json</t>
         </is>
       </c>
     </row>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0007.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0007.png</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0007.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0007.json</t>
         </is>
       </c>
     </row>
@@ -8425,12 +8425,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0006.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0006.png</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0006.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0006.json</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0005.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0005.png</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0005.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0005.json</t>
         </is>
       </c>
     </row>
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0013.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0013.png</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0013.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0013.json</t>
         </is>
       </c>
     </row>
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0012.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0012.png</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0012.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0012.json</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8681,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0018.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0018.png</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0018.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0018.json</t>
         </is>
       </c>
     </row>
@@ -8745,12 +8745,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0020.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0020.png</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0020.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0020.json</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0003.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0003.png</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0003.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0003.json</t>
         </is>
       </c>
     </row>
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0009.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0009.png</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0009.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0009.json</t>
         </is>
       </c>
     </row>
@@ -8937,12 +8937,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0010.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0010.png</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0010.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0010.json</t>
         </is>
       </c>
     </row>
@@ -9001,12 +9001,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0022.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0022.png</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0022.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0022.json</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0014.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0014.png</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0014.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0014.json</t>
         </is>
       </c>
     </row>
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0000.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0000.png</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0000.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0000.json</t>
         </is>
       </c>
     </row>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0017.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0017.png</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0017.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0017.json</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9257,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0011.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0011.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0011.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0011.json</t>
         </is>
       </c>
     </row>

--- a/task-reviews/puzzles/task_puzzles_arithmetic_grid_value/task_puzzles_arithmetic_grid_value.xlsx
+++ b/task-reviews/puzzles/task_puzzles_arithmetic_grid_value/task_puzzles_arithmetic_grid_value.xlsx
@@ -4285,7 +4285,199 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>254366805179653</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0001.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="228" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 516.0, 684.0, 616.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 516.0, 684.0, 616.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1272804547660839</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0003.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="228" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 392.0, 540.0, 492.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 392.0, 540.0, 492.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1347669799959681</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0014.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="228" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
@@ -4293,63 +4485,63 @@
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 144.0, 540.0, 244.0]], "answer": 19}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 144.0, 540.0, 244.0]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 578.0, 540.0, 678.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 578.0, 540.0, 678.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>37125808579783</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0013.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0013.json</t>
+      <c r="K5" t="n">
+        <v>1906614857508960</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0017.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0017.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="228" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="6" ht="228" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>difference_rule_missing</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer format: set "answer" to the exact integer value requested by the puzzle.
@@ -4357,63 +4549,255 @@
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
 Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 330.0, 396.0, 430.0]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 330.0, 396.0, 430.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1916877378031270</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0016.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="228" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1987185184149683</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0009.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="228" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2818163226170135</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0005.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="228" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 22}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>[[420.0, 206.0, 540.0, 306.0]]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>561384256667613</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0009.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0009.json</t>
+      <c r="K9" t="n">
+        <v>3066338664111535</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0020.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="228" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="10" ht="228" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>difference_rule_missing</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer field: set "answer" to the exact integer value requested by the puzzle.
@@ -4421,63 +4805,383 @@
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 15}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3301053754152527</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0006.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="228" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 330.0, 684.0, 430.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 330.0, 684.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 268.0, 684.0, 368.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 268.0, 684.0, 368.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>788921655544065</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0021.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0021.json</t>
+      <c r="K11" t="n">
+        <v>3398181041593032</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0022.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0022.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="228" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="12" ht="228" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>difference_rule_missing</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 268.0, 396.0, 368.0]], "answer": 23}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 268.0, 396.0, 368.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3459141979332527</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0024.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="228" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 18}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3759048811713935</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0002.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="228" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 24}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3971362623469193</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0019.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="228" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4908592885069005</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0023.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="228" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer: set "answer" to the exact integer value requested by the puzzle.
@@ -4485,63 +5189,63 @@
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 330.0, 396.0, 430.0]], "answer": 18}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 330.0, 396.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1235092336211076</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0006.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0006.json</t>
+      <c r="K16" t="n">
+        <v>5292654261217386</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0007.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0007.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="228" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="17" ht="228" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>difference_rule_missing</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Solve the repeated row rule and report the missing integer.
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer field: set "answer" to the exact integer value requested by the puzzle.
@@ -4549,63 +5253,383 @@
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Solve the repeated row rule and report the missing integer.
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 24}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1424090869005855</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0000.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0000.json</t>
+      <c r="K17" t="n">
+        <v>5635807119194425</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0015.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0015.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="228" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="18" ht="228" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>difference_rule_missing</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 206.0, 684.0, 306.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 206.0, 684.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6258338672818792</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0008.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="228" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 392.0, 396.0, 492.0]], "answer": 11}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 392.0, 396.0, 492.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6850443688695066</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0011.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="228" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 330.0, 540.0, 430.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 330.0, 540.0, 430.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6951970214580056</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0012.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="228" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 268.0, 684.0, 368.0]], "answer": 13}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 268.0, 684.0, 368.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7099311912746240</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0004.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="228" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>7574282091456154</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0021.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="228" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>difference_rule_missing</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer field: set "answer" to the exact integer value requested by the puzzle.
@@ -4613,191 +5637,127 @@
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 516.0, 396.0, 616.0]], "answer": 16}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 516.0, 396.0, 616.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2049665620802028</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0017.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="228" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 392.0, 684.0, 492.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 392.0, 684.0, 492.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 14}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>2621035039674862</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0024.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0024.json</t>
+      <c r="K23" t="n">
+        <v>7754872745190085</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0013.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0013.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="228" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="24" ht="228" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>difference_rule_missing</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
+Answer field: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 268.0, 684.0, 368.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 268.0, 684.0, 368.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>2824876357593152</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0014.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0014.json</t>
+      <c r="K24" t="n">
+        <v>8602615175570150</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0010.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0010.json</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="228" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
+    <row r="25" ht="228" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>difference_rule_missing</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer field: set "answer" to the exact integer value requested by the puzzle.
@@ -4805,255 +5765,63 @@
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 14}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>3005456018788492</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0012.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0012.json</t>
+      <c r="K25" t="n">
+        <v>8992519151177022</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0018.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0018.json</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="228" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
+    <row r="26" ht="228" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>difference_rule_missing</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 82.0, 540.0, 182.0]], "answer": 13}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 82.0, 540.0, 182.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3116505826913037</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0001.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="228" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3283922293646655</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0002.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="228" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 20}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>5015965148735339</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0008.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0008.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="228" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer format: set "answer" to the exact integer value requested by the puzzle.
@@ -5061,777 +5829,9 @@
 {"evidence":[[420,250,540,350]],"answer":6}</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5194719760855957</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0007.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="228" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>5431679585362227</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0019.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="228" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 330.0, 684.0, 430.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 330.0, 684.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>5549375648018629</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0015.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="228" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 144.0, 684.0, 244.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 144.0, 684.0, 244.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5704091339313634</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0023.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="228" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 206.0, 684.0, 306.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 206.0, 684.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>5799854668923118</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0011.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="228" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 15}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6278879575218717</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0016.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="228" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 15}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>6473825806136667</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0018.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="228" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 578.0, 540.0, 678.0]], "answer": 15}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 578.0, 540.0, 678.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7056277765585188</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0010.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="228" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 82.0, 684.0, 182.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 82.0, 684.0, 182.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7362391605482940</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0020.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="228" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 22}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8273873187393038</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0004.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="228" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 144.0, 684.0, 244.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 144.0, 684.0, 244.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8494182065235398</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0022.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="228" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 330.0, 396.0, 430.0]], "answer": 24}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 330.0, 396.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8737336667927718</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0003.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="228" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>difference_rule_missing</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":6}</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
@@ -5840,12 +5840,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[564.0, 144.0, 684.0, 244.0]], "answer": 6}</t>
+          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 13}</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>[[564.0, 144.0, 684.0, 244.0]]</t>
+          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -5859,16 +5859,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>8961430089163895</v>
+        <v>8998482647136489</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0005.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/difference_rule_missing/0000.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0005.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/difference_rule_missing/0000.json</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer field: set "answer" to the exact integer value requested by the puzzle.
@@ -5992,16 +5992,16 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{"evidence": [[420.0, 82.0, 540.0, 182.0]], "answer": 2}</t>
+          <t>{"evidence": [[420.0, 82.0, 540.0, 182.0]], "answer": 4}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -6020,16 +6020,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>231551026633990</v>
+        <v>166596309150462</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0004.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0007.png</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0004.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0007.json</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,135 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 144.0, 396.0, 244.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 144.0, 396.0, 244.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>261528791975511</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0016.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="228" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 144.0, 684.0, 244.0]], "answer": 24}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 144.0, 684.0, 244.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1304759103590426</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0015.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="228" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
@@ -6054,63 +6182,255 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 144.0, 684.0, 244.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 144.0, 684.0, 244.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2075567722127862</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0003.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="228" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 206.0, 684.0, 306.0]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 206.0, 684.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2177107113326015</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0012.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="228" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2490026985975276</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0010.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="228" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 330.0, 684.0, 430.0]], "answer": 21}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 330.0, 684.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 392.0, 396.0, 492.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 392.0, 396.0, 492.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>354210566355604</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0001.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0001.json</t>
+      <c r="K8" t="n">
+        <v>2669936518414364</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0005.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0005.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="228" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="9" ht="228" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>product_rule_missing</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer field: set "answer" to the exact integer value requested by the puzzle.
@@ -6118,63 +6438,127 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1884884364630883</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0012.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0012.json</t>
+      <c r="K9" t="n">
+        <v>2694837084293984</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0018.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0018.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="228" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="10" ht="228" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>product_rule_missing</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2970409412568510</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0009.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="228" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer format: set "answer" to the exact integer value requested by the puzzle.
@@ -6182,63 +6566,255 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 330.0, 684.0, 430.0]], "answer": 20}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 330.0, 684.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>2035712891245446</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0002.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0002.json</t>
+      <c r="K11" t="n">
+        <v>3007597030355573</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0014.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0014.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="228" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="12" ht="228" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>product_rule_missing</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 268.0, 684.0, 368.0]], "answer": 24}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 268.0, 684.0, 368.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3819632534875592</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0011.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="228" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3976703600658235</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0006.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="228" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 206.0, 684.0, 306.0]], "answer": 14}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 206.0, 684.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4031784628554153</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0021.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="228" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
@@ -6246,127 +6822,127 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4076920107130196</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0004.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="228" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 18}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>2189852464468987</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0024.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0024.json</t>
+      <c r="K16" t="n">
+        <v>4083987597672878</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0002.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0002.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="228" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="17" ht="228" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>product_rule_missing</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2380803696922209</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0022.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="228" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Solve the repeated row rule and report the missing integer.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
@@ -6374,63 +6950,63 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Solve the repeated row rule and report the missing integer.
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
+Answer: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 392.0, 540.0, 492.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 392.0, 540.0, 492.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 392.0, 396.0, 492.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 392.0, 396.0, 492.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>2710748875818121</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0018.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0018.json</t>
+      <c r="K17" t="n">
+        <v>4725399801248610</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0017.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0017.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="228" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="18" ht="228" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>product_rule_missing</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What number should replace the question mark?
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer: set "answer" to the exact integer value requested by the puzzle.
@@ -6438,63 +7014,383 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What number should replace the question mark?
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 18}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>4907480491943190</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0000.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="228" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 24}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5311813936924766</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0019.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="228" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5971633161375757</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0024.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="228" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 18}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6928587190966320</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0008.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="228" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 206.0, 684.0, 306.0]], "answer": 22}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 206.0, 684.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 82.0, 540.0, 182.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 82.0, 540.0, 182.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>2940254838841452</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0021.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0021.json</t>
+      <c r="K22" t="n">
+        <v>7408898273417759</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0013.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0013.json</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="228" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
+    <row r="23" ht="228" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>product_rule_missing</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":8}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":8}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>8017086745839419</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0022.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="228" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>product_rule_missing</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Find the missing number in the arithmetic grid.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer format: set "answer" to the exact integer value requested by the puzzle.
@@ -6502,127 +7398,63 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Find the missing number in the arithmetic grid.
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 330.0, 396.0, 430.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 330.0, 396.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 578.0, 684.0, 678.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 578.0, 684.0, 678.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>3582148368372712</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0007.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0007.json</t>
+      <c r="K24" t="n">
+        <v>8153458424695833</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0001.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0001.json</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="228" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
+    <row r="25" ht="228" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>product_rule_missing</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 268.0, 684.0, 368.0]], "answer": 20}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 268.0, 684.0, 368.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3706965351746386</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0010.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="228" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Find the missing number in the arithmetic grid.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer rule: set "answer" to the exact integer value requested by the puzzle.
@@ -6630,383 +7462,63 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Find the missing number in the arithmetic grid.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 268.0, 396.0, 368.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 268.0, 396.0, 368.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 392.0, 396.0, 492.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 392.0, 396.0, 492.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>4162341951343025</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0008.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0008.json</t>
+      <c r="K25" t="n">
+        <v>8620751406856509</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0023.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0023.json</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="228" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
+    <row r="26" ht="228" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>product_rule_missing</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>4517167075562665</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0003.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="228" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5218270328423963</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0014.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="228" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>5568248730406821</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0009.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="228" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 330.0, 540.0, 430.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 330.0, 540.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>5825453961836329</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0019.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="228" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 330.0, 396.0, 430.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 330.0, 396.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>6942930526492875</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0016.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="228" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
@@ -7014,558 +7526,46 @@
 {"evidence":[[420,250,540,350]],"answer":8}</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact integer value requested by the puzzle.
+Answer: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":8}</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 578.0, 540.0, 678.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 578.0, 540.0, 678.0]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>6979971666820415</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0013.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="228" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 330.0, 396.0, 430.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 330.0, 396.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>7363356909694873</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0005.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="228" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 18}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7597195539127556</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0000.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="228" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 392.0, 396.0, 492.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 392.0, 396.0, 492.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7834062777526155</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0015.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="228" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>8013044905864393</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0011.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="228" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 578.0, 540.0, 678.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 578.0, 540.0, 678.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8053737615914846</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="K26" t="n">
+        <v>8902258178178830</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0020.png</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="228" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 330.0, 540.0, 430.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 330.0, 540.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8560496084652403</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0017.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="228" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8593430741230953</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0023.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="228" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>product_rule_missing</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":8}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":8}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 268.0, 396.0, 368.0]], "answer": 6}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 268.0, 396.0, 368.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>8992429694823590</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/product_rule_missing/0006.png</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/product_rule_missing/0006.json</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,263 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 516.0, 396.0, 616.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 516.0, 396.0, 616.0]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>165920796137853</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0020.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0020.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="228" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 330.0, 396.0, 430.0]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 330.0, 396.0, 430.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>299088485352120</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0019.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="228" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 330.0, 684.0, 430.0]], "answer": 24}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 330.0, 684.0, 430.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>575526261257351</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0001.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="228" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 14}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>721560175992575</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0000.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="228" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Find the missing number in the arithmetic grid.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer rule: set "answer" to the exact integer value requested by the puzzle.
@@ -7687,63 +7943,1151 @@
 {"evidence":[[420,250,540,350]],"answer":7}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Find the missing number in the arithmetic grid.
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":7}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 82.0, 540.0, 182.0]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 144.0, 540.0, 244.0]], "answer": 13}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 144.0, 540.0, 244.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>721658839907947</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0013.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="228" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 82.0, 396.0, 182.0]], "answer": 13}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 82.0, 396.0, 182.0]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>964941301877785</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0014.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="228" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 82.0, 396.0, 182.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 82.0, 396.0, 182.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1045728190275244</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0002.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="228" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 330.0, 684.0, 430.0]], "answer": 23}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 330.0, 684.0, 430.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1299583092857566</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0008.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="228" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 578.0, 684.0, 678.0]], "answer": 16}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 578.0, 684.0, 678.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1641294425012306</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0022.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="228" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 578.0, 396.0, 678.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 578.0, 396.0, 678.0]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1905168070753650</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0006.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="228" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2732564595296320</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0011.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="228" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Find the missing number in the arithmetic grid.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 268.0, 540.0, 368.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 268.0, 540.0, 368.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3187039591518860</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0023.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="228" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 392.0, 540.0, 492.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 392.0, 540.0, 492.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3372620525633685</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0017.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="228" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3714394222604930</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0004.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="228" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>You are given an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 144.0, 540.0, 244.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 144.0, 540.0, 244.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4495601232022726</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0010.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="228" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>6387117525936276</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0016.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="228" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 144.0, 396.0, 244.0]], "answer": 19}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 144.0, 396.0, 244.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6464676730780526</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0005.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="228" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 21}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6560892287321003</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0003.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="228" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 330.0, 540.0, 430.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 330.0, 540.0, 430.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>7521216506459560</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0018.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="228" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer field: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 578.0, 540.0, 678.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[420.0, 578.0, 540.0, 678.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7707875272394908</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0009.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="228" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Find the missing number in the arithmetic grid.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Find the missing number in the arithmetic grid.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[420.0, 82.0, 540.0, 182.0]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>[[420.0, 82.0, 540.0, 182.0]]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>490363739178462</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="K22" t="n">
+        <v>7716565980299449</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0015.png</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0015.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="228" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="23" ht="228" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>sum_rule_missing</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
+Answer rule: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"evidence":[[420,250,540,350]],"answer":7}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>The image shows an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Solve the repeated row rule and report the missing integer.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact integer value requested by the puzzle.
+Example JSON:
+{"answer":7}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 454.0, 396.0, 554.0]], "answer": 11}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 454.0, 396.0, 554.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>7759932187217264</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0012.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0012.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="228" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_puzzles_arithmetic_grid_value</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>sum_rule_missing</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
@@ -7751,191 +9095,63 @@
 {"evidence":[[420,250,540,350]],"answer":7}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What integer completes the question-mark grid cell?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 82.0, 396.0, 182.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 82.0, 396.0, 182.0]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>539771132417753</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0024.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="228" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What integer completes the question-mark grid cell?
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Solve the repeated row rule and report the missing integer.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":7}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 516.0, 540.0, 616.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 516.0, 540.0, 616.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>846429320371294</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0001.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0001.json</t>
+      <c r="K24" t="n">
+        <v>8211055415325569</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0024.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0024.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="228" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="25" ht="228" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>sum_rule_missing</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. What integer completes the question-mark grid cell?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 516.0, 684.0, 616.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 516.0, 684.0, 616.0]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1094591482966115</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0021.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="228" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
@@ -7943,319 +9159,63 @@
 {"evidence":[[420,250,540,350]],"answer":7}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":7}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 14}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 578.0, 396.0, 678.0]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 578.0, 396.0, 678.0]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>2214128473327955</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0008.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0008.json</t>
+      <c r="K25" t="n">
+        <v>8259368469472499</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0007.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0007.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="228" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="26" ht="228" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_puzzles_arithmetic_grid_value</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>sum_rule_missing</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 82.0, 396.0, 182.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 82.0, 396.0, 182.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2363175258457251</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0002.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="228" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 330.0, 396.0, 430.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 330.0, 396.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2458544191683771</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0016.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="228" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 454.0, 684.0, 554.0]], "answer": 18}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 454.0, 684.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2773427567350739</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0004.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="228" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 144.0, 684.0, 244.0]], "answer": 19}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 144.0, 684.0, 244.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2838918379965839</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0023.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="228" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
@@ -8263,1006 +9223,46 @@
 {"evidence":[[420,250,540,350]],"answer":7}</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Read the number grid and infer the value of the question-mark cell. What number should replace the question mark?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact integer value requested by the puzzle.
 Example JSON:
 {"answer":7}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 578.0, 684.0, 678.0]], "answer": 23}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 578.0, 684.0, 678.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[276.0, 516.0, 396.0, 616.0]], "answer": 18}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[276.0, 516.0, 396.0, 616.0]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>3182290824654566</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0019.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="228" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3236573177034340</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0007.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="228" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3976103736634413</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0006.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="228" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 392.0, 684.0, 492.0]], "answer": 21}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 392.0, 684.0, 492.0]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4122174509689330</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0005.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="228" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4888588356041452</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0013.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="228" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>You are given an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 268.0, 396.0, 368.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 268.0, 396.0, 368.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>5450225061764271</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0012.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="228" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 13}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>6036900418125689</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0018.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="228" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 454.0, 540.0, 554.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 454.0, 540.0, 554.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6411444177985800</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0020.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="228" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 268.0, 540.0, 368.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 268.0, 540.0, 368.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>6495120706100842</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0003.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="228" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. What integer completes the question-mark grid cell?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 578.0, 396.0, 678.0]], "answer": 19}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 578.0, 396.0, 678.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7572854455918237</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0009.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="228" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 516.0, 540.0, 616.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 516.0, 540.0, 616.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7955238996842657</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0010.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="228" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Use the arithmetic puzzle grid in the image: an outline-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the repeated row rule to determine the missing number. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[420.0, 206.0, 540.0, 306.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[420.0, 206.0, 540.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7979087518427831</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0022.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="228" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>You are given a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. What number should replace the question mark?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 330.0, 684.0, 430.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 330.0, 684.0, 430.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8016936283778570</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0014.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="228" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Solve the arithmetic grid puzzle and report the missing integer. Determine the value that belongs in the question-mark cell.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[564.0, 268.0, 684.0, 368.0]], "answer": 24}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[564.0, 268.0, 684.0, 368.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8850184221075859</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0000.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="228" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Look at the arithmetic grid puzzle in the image: an arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Work from the arithmetic rule repeated across rows to find the missing number. Find the missing number in the arithmetic grid.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 19}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8865117130943544</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0017.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="228" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_puzzles_arithmetic_grid_value</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>sum_rule_missing</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the question-mark grid cell.
-Answer field: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"evidence":[[420,250,540,350]],"answer":7}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the arithmetic number grid shown in the image: a card-style arithmetic puzzle grid with 3 columns and 3 to 5 rows of boxed integers, where one cell shows a question mark instead of a number. Use the visible rows to solve for the question-mark grid cell. Solve the repeated row rule and report the missing integer.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact integer value requested by the puzzle.
-Example JSON:
-{"answer":7}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[276.0, 206.0, 396.0, 306.0]], "answer": 22}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[276.0, 206.0, 396.0, 306.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8890763150615891</v>
+        <v>8280978240694840</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0011.png</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/images/sum_rule_missing/0021.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0011.json</t>
+          <t>puzzles/task_puzzles_arithmetic_grid_value/data/sum_rule_missing/0021.json</t>
         </is>
       </c>
     </row>
